--- a/src/main/resources/templates/xlsx/1차전형결과.xlsx
+++ b/src/main/resources/templates/xlsx/1차전형결과.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10311"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29825"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jeon-yujin/Documents/workspace/backend/springboot/maru/src/main/resources/templates/xlsx/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{851CB714-6559-5E4A-832A-5C8BB5C4FBD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3448E8E4-EFFF-47CE-8B4E-AB02B7DC4F42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="15240" yWindow="740" windowWidth="15000" windowHeight="18900" xr2:uid="{7690012B-BFFA-3C48-824D-509550F219F4}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,58 +36,68 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+  <si>
+    <t>접수번호</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
   <si>
     <t>수험번호</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>전형 구분</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>전형 결과</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>지원자</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>점수</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>지원 전형</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>최종 전형</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>이름</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>전형 구분</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>접수번호</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>지원자</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>지원 전형</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>최종 전형</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>전형 결과</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>성별</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>생년월일</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>지원자 전화번호</t>
+  </si>
+  <si>
+    <t>보호자 전화번호</t>
+  </si>
+  <si>
+    <t>출신지역</t>
+  </si>
+  <si>
+    <t>졸업 구분</t>
+  </si>
+  <si>
     <t>출신 학교</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>출신 지역</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>졸업 구분</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>점수</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>학교 코드</t>
   </si>
   <si>
     <t>교과성적</t>
@@ -107,14 +117,6 @@
   </si>
   <si>
     <t>총점</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>학교 코드</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>생년월일</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -270,9 +272,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 테마">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -310,7 +312,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -416,7 +418,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -558,7 +560,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -566,37 +568,39 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C8EB960-16E4-4546-BE22-CABF45F1D2EB}">
-  <dimension ref="A1:Q2"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="18"/>
+  <dimension ref="A1:S2"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="17.25" customHeight="1"/>
   <cols>
-    <col min="1" max="2" width="9.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="31.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="5.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="21.7109375" customWidth="1"/>
-    <col min="9" max="9" width="21.85546875" customWidth="1"/>
-    <col min="10" max="10" width="16" customWidth="1"/>
-    <col min="11" max="11" width="16.5703125" customWidth="1"/>
-    <col min="12" max="12" width="9.5703125" customWidth="1"/>
-    <col min="13" max="15" width="9" customWidth="1"/>
-    <col min="16" max="16" width="7.42578125" customWidth="1"/>
-    <col min="17" max="17" width="9.42578125" customWidth="1"/>
+    <col min="1" max="2" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="31.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="21.6640625" customWidth="1"/>
+    <col min="9" max="9" width="21.88671875" customWidth="1"/>
+    <col min="10" max="10" width="21" customWidth="1"/>
+    <col min="11" max="11" width="20.5546875" customWidth="1"/>
+    <col min="12" max="12" width="15.33203125" customWidth="1"/>
+    <col min="13" max="13" width="14.88671875" customWidth="1"/>
+    <col min="14" max="14" width="15.21875" customWidth="1"/>
+    <col min="15" max="17" width="9" customWidth="1"/>
+    <col min="18" max="18" width="7.44140625" customWidth="1"/>
+    <col min="19" max="19" width="9.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="30" customHeight="1">
+    <row r="1" spans="1:19" ht="30" customHeight="1">
       <c r="A1" s="2" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="2"/>
       <c r="E1" s="2" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F1" s="3" t="s">
         <v>4</v>
@@ -606,70 +610,78 @@
       <c r="I1" s="4"/>
       <c r="J1" s="4"/>
       <c r="K1" s="4"/>
-      <c r="L1" s="5"/>
-      <c r="M1" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="4"/>
-      <c r="O1" s="4"/>
+      <c r="L1" s="4"/>
+      <c r="M1" s="4"/>
+      <c r="N1" s="5"/>
+      <c r="O1" s="3" t="s">
+        <v>5</v>
+      </c>
       <c r="P1" s="4"/>
-      <c r="Q1" s="5"/>
+      <c r="Q1" s="4"/>
+      <c r="R1" s="4"/>
+      <c r="S1" s="5"/>
     </row>
-    <row r="2" spans="1:17" ht="30" customHeight="1">
+    <row r="2" spans="1:19" ht="30" customHeight="1">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="C2" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q2" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="I2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="O2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="P2" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="Q2" s="1" t="s">
-        <v>17</v>
+      <c r="R2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="6">
+    <mergeCell ref="O1:S1"/>
+    <mergeCell ref="F1:N1"/>
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:D1"/>
     <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:L1"/>
-    <mergeCell ref="M1:Q1"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
